--- a/Du_Lieu_Mau_He_Thong/1_File_Excel_XLSX/Bieu_mau_de_nghi_vay_von_va_phuong_an_tra_no_kiem_cam_ket_tai_san.xlsx
+++ b/Du_Lieu_Mau_He_Thong/1_File_Excel_XLSX/Bieu_mau_de_nghi_vay_von_va_phuong_an_tra_no_kiem_cam_ket_tai_san.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataSheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,10 +33,10 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000843D"/>
         <bgColor rgb="0000843D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F9F5"/>
+        <bgColor rgb="00F4F9F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,13 +82,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,17 +464,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kỳ thanh toán</t>
@@ -472,207 +487,170 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gốc phải trả (VND)</t>
+          <t>Tiền gốc trả hàng tháng (VND)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Tiền lãi tạm tính (6.8%/năm)</t>
+          <t>Tiền lãi tạm tính 6.8%/năm (VND)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Tổng tiền trả kỳ (VND)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Tổng số tiền trả kỳ (VND)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Kỳ 1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>1,500,000,000</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>12,500,000</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>8,500,000</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>21,000,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B2" s="3" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>21000000</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Kỳ 2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>1,487,500,000</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>12,500,000</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>8,429,167</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>20,929,167</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3" s="5" t="n">
+        <v>1487500000</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>8429167</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>20929167</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Kỳ 3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>1,475,000,000</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12,500,000</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,358,333</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,858,333</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="B4" s="3" t="n">
+        <v>1475000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>8358333</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>20858333</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Kỳ 4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1,462,500,000</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,500,000</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8,287,500</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20,787,500</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="5" t="n">
+        <v>1462500000</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>8287500</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>20787500</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Kỳ 5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>1,450,000,000</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12,500,000</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,216,667</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20,716,667</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B6" s="3" t="n">
+        <v>1450000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>8216667</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>20716667</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Kỳ 6</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1437500000</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8145833</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>20645833</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Kỳ 12</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1362500000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>7720833</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>20220833</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>Kỳ 120</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>12,500,000</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,500,000</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>70,833</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,570,833</t>
-        </is>
+      <c r="B9" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>70833</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>12570833</v>
       </c>
     </row>
   </sheetData>
